--- a/downloads/indicadores/TASA/TASA_datos.xlsx
+++ b/downloads/indicadores/TASA/TASA_datos.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L109"/>
+  <dimension ref="A1:L108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6548,64 +6548,6 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="7" t="inlineStr">
-        <is>
-          <t>Ago 26</t>
-        </is>
-      </c>
-      <c r="B109" s="8" t="n">
-        <v>46235</v>
-      </c>
-      <c r="C109" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="D109" s="7" t="inlineStr">
-        <is>
-          <t>+0.0 pp</t>
-        </is>
-      </c>
-      <c r="E109" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F109" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G109" s="7" t="inlineStr">
-        <is>
-          <t>Porcentaje anual</t>
-        </is>
-      </c>
-      <c r="H109" s="7" t="inlineStr">
-        <is>
-          <t>No aplica</t>
-        </is>
-      </c>
-      <c r="I109" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="J109" s="7" t="inlineStr">
-        <is>
-          <t>Banco de México (SIE)</t>
-        </is>
-      </c>
-      <c r="K109" s="7" t="inlineStr">
-        <is>
-          <t>https://www.banxico.org.mx/mercados/tasas-de-referencia.html</t>
-        </is>
-      </c>
-      <c r="L109" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:L3"/>

--- a/downloads/indicadores/TASA/TASA_datos.xlsx
+++ b/downloads/indicadores/TASA/TASA_datos.xlsx
@@ -18,7 +18,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0&quot;%&quot;"/>
   </numFmts>
   <fonts count="5">
     <font>

--- a/downloads/indicadores/TASA/TASA_datos.xlsx
+++ b/downloads/indicadores/TASA/TASA_datos.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:G109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3943,6 +3943,39 @@
         </is>
       </c>
     </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>Ago 26</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C109" s="8" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D109" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="E109" s="9" t="inlineStr">
+        <is>
+          <t>Banco de México (SIE)</t>
+        </is>
+      </c>
+      <c r="F109" s="9" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/mercados/tasas-de-referencia.html</t>
+        </is>
+      </c>
+      <c r="G109" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:G3"/>
